--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKStillstatus.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKStillstatus.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-23</t>
+    <t>2025-12-11</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1217,13 +1217,17 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>Bedeutung: Erfasster Wert der Observation.</t>
+    <t>**Begründung Must-Support:** Erfasster Wert der Observation.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/isik/ValueSet/StillstatusVS</t>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1240,6 +1244,34 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>**Begründung Must-Support:** Viele Lebenszustände (z. B. Schwangerschaftsstatus, Alkoholabusus, Raucherstatus) werden als kategorisierte Angaben kodiert und erfordern daher ein CodeableConcept.</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/isik/ValueSet/StillstatusVS</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>**Begründung Must-Support:** Zeitpunktbezogene Lebenszustände (z. B. erwarteter Entbindungstermin) benötigen eine eindeutige Datumsangabe als Wert.</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2053,12 +2085,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP77"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -7881,7 +7913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>375</v>
       </c>
@@ -7946,26 +7978,26 @@
         <v>17</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>17</v>
+      </c>
       <c r="Z49" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AB49" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AA49" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>17</v>
-      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>17</v>
+        <v>381</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>375</v>
@@ -7977,7 +8009,7 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>100</v>
@@ -7986,62 +8018,64 @@
         <v>17</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>17</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>236</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>17</v>
@@ -8066,14 +8100,12 @@
         <v>17</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y50" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y50" s="2"/>
+      <c r="Z50" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>17</v>
       </c>
@@ -8090,7 +8122,7 @@
         <v>17</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8099,7 +8131,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -8108,62 +8140,64 @@
         <v>17</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>17</v>
+        <v>383</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>187</v>
+        <v>384</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>17</v>
+        <v>386</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D51" t="s" s="2">
-        <v>396</v>
+        <v>17</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>236</v>
+        <v>394</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>17</v>
@@ -8188,13 +8222,13 @@
         <v>17</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>401</v>
+        <v>17</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>402</v>
+        <v>17</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>17</v>
@@ -8212,16 +8246,16 @@
         <v>17</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>100</v>
@@ -8230,27 +8264,27 @@
         <v>17</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>406</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8261,7 +8295,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>17</v>
@@ -8273,19 +8307,19 @@
         <v>17</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>408</v>
+        <v>236</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>17</v>
@@ -8310,13 +8344,13 @@
         <v>17</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>17</v>
+        <v>401</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>17</v>
+        <v>402</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>17</v>
@@ -8334,16 +8368,16 @@
         <v>17</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>17</v>
+        <v>403</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>100</v>
@@ -8355,10 +8389,10 @@
         <v>17</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>187</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>17</v>
@@ -8369,21 +8403,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>17</v>
+        <v>406</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>17</v>
@@ -8398,15 +8432,17 @@
         <v>236</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>17</v>
       </c>
@@ -8430,13 +8466,13 @@
         <v>17</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>17</v>
@@ -8454,13 +8490,13 @@
         <v>17</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>17</v>
@@ -8472,27 +8508,27 @@
         <v>17</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8503,7 +8539,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>17</v>
@@ -8515,19 +8551,19 @@
         <v>17</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>236</v>
+        <v>418</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>17</v>
@@ -8552,13 +8588,13 @@
         <v>17</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>430</v>
+        <v>17</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>431</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>17</v>
@@ -8576,13 +8612,13 @@
         <v>17</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>17</v>
@@ -8597,10 +8633,10 @@
         <v>17</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>17</v>
@@ -8611,10 +8647,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8637,16 +8673,16 @@
         <v>17</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>435</v>
+        <v>236</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8672,13 +8708,13 @@
         <v>17</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>17</v>
+        <v>429</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>17</v>
+        <v>430</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>17</v>
@@ -8696,7 +8732,7 @@
         <v>17</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8714,27 +8750,27 @@
         <v>17</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8757,18 +8793,20 @@
         <v>17</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>444</v>
+        <v>236</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>17</v>
       </c>
@@ -8792,13 +8830,13 @@
         <v>17</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>17</v>
+        <v>440</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>17</v>
+        <v>441</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>17</v>
@@ -8816,7 +8854,7 @@
         <v>17</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8834,27 +8872,27 @@
         <v>17</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>448</v>
+        <v>17</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>451</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8865,7 +8903,7 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>17</v>
@@ -8877,20 +8915,18 @@
         <v>17</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>17</v>
       </c>
@@ -8938,45 +8974,45 @@
         <v>17</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8999,15 +9035,17 @@
         <v>17</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>102</v>
+        <v>454</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>103</v>
+        <v>455</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>17</v>
@@ -9056,7 +9094,7 @@
         <v>17</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -9068,25 +9106,25 @@
         <v>17</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>17</v>
+        <v>459</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>17</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9098,7 +9136,7 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9117,18 +9155,20 @@
         <v>17</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>109</v>
+        <v>463</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>110</v>
+        <v>464</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>111</v>
+        <v>465</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>17</v>
       </c>
@@ -9176,7 +9216,7 @@
         <v>17</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>116</v>
+        <v>462</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9188,7 +9228,7 @@
         <v>17</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>117</v>
+        <v>468</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>17</v>
@@ -9197,10 +9237,10 @@
         <v>17</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>17</v>
+        <v>469</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>106</v>
+        <v>470</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>17</v>
@@ -9211,46 +9251,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>464</v>
+        <v>17</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>465</v>
+        <v>103</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>17</v>
       </c>
@@ -9298,19 +9334,19 @@
         <v>17</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>17</v>
@@ -9322,7 +9358,7 @@
         <v>17</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>17</v>
@@ -9333,21 +9369,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>17</v>
@@ -9359,15 +9395,17 @@
         <v>17</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>469</v>
+        <v>109</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>110</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>17</v>
@@ -9416,19 +9454,19 @@
         <v>17</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>116</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>472</v>
+        <v>17</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>17</v>
@@ -9437,10 +9475,10 @@
         <v>17</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>473</v>
+        <v>17</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>474</v>
+        <v>106</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>17</v>
@@ -9451,42 +9489,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>17</v>
+        <v>474</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>469</v>
+        <v>109</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="N62" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>17</v>
       </c>
@@ -9534,19 +9576,19 @@
         <v>17</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>472</v>
+        <v>17</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>17</v>
@@ -9555,10 +9597,10 @@
         <v>17</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>473</v>
+        <v>17</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>478</v>
+        <v>187</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>17</v>
@@ -9569,10 +9611,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9595,7 +9637,7 @@
         <v>17</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>236</v>
+        <v>479</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>480</v>
@@ -9603,12 +9645,8 @@
       <c r="M63" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>483</v>
-      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>17</v>
       </c>
@@ -9632,13 +9670,13 @@
         <v>17</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>484</v>
+        <v>17</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>485</v>
+        <v>17</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>17</v>
@@ -9656,7 +9694,7 @@
         <v>17</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9665,7 +9703,7 @@
         <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>17</v>
+        <v>482</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>100</v>
@@ -9674,13 +9712,13 @@
         <v>17</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>486</v>
+        <v>17</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>405</v>
+        <v>484</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>17</v>
@@ -9691,10 +9729,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9705,7 +9743,7 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>17</v>
@@ -9717,20 +9755,16 @@
         <v>17</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>236</v>
+        <v>479</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>17</v>
       </c>
@@ -9754,13 +9788,13 @@
         <v>17</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>493</v>
+        <v>17</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>494</v>
+        <v>17</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>17</v>
@@ -9778,16 +9812,16 @@
         <v>17</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>17</v>
+        <v>482</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>100</v>
@@ -9796,13 +9830,13 @@
         <v>17</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>486</v>
+        <v>17</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>405</v>
+        <v>488</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>17</v>
@@ -9813,10 +9847,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9839,17 +9873,19 @@
         <v>17</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>17</v>
@@ -9874,13 +9910,13 @@
         <v>17</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>17</v>
+        <v>494</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>17</v>
+        <v>495</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>17</v>
@@ -9898,7 +9934,7 @@
         <v>17</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9916,13 +9952,13 @@
         <v>17</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>17</v>
+        <v>496</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>17</v>
+        <v>497</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>500</v>
+        <v>415</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>17</v>
@@ -9933,10 +9969,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9947,7 +9983,7 @@
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>17</v>
@@ -9959,16 +9995,20 @@
         <v>17</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>17</v>
       </c>
@@ -9992,13 +10032,13 @@
         <v>17</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>17</v>
+        <v>503</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>17</v>
+        <v>504</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>17</v>
@@ -10016,13 +10056,13 @@
         <v>17</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>17</v>
@@ -10034,13 +10074,13 @@
         <v>17</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>17</v>
+        <v>496</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>504</v>
+        <v>415</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>17</v>
@@ -10065,7 +10105,7 @@
         <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>17</v>
@@ -10074,7 +10114,7 @@
         <v>17</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>506</v>
@@ -10085,10 +10125,10 @@
       <c r="M67" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>17</v>
       </c>
@@ -10142,7 +10182,7 @@
         <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>17</v>
@@ -10157,10 +10197,10 @@
         <v>17</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>17</v>
@@ -10171,10 +10211,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10185,7 +10225,7 @@
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>17</v>
@@ -10194,20 +10234,18 @@
         <v>17</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>516</v>
-      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>17</v>
@@ -10256,13 +10294,13 @@
         <v>17</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>17</v>
@@ -10277,10 +10315,10 @@
         <v>17</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>17</v>
@@ -10291,10 +10329,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10317,20 +10355,18 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>453</v>
+        <v>516</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>522</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>17</v>
       </c>
@@ -10378,7 +10414,7 @@
         <v>17</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10399,10 +10435,10 @@
         <v>17</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>17</v>
@@ -10413,10 +10449,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10427,7 +10463,7 @@
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>17</v>
@@ -10436,18 +10472,20 @@
         <v>17</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>102</v>
+        <v>523</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>103</v>
+        <v>524</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>17</v>
@@ -10496,19 +10534,19 @@
         <v>17</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>17</v>
@@ -10517,10 +10555,10 @@
         <v>17</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>17</v>
+        <v>520</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>106</v>
+        <v>527</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>17</v>
@@ -10531,14 +10569,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10554,21 +10592,23 @@
         <v>17</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>109</v>
+        <v>463</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>110</v>
+        <v>529</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>111</v>
+        <v>530</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>17</v>
       </c>
@@ -10616,7 +10656,7 @@
         <v>17</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>116</v>
+        <v>528</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10628,7 +10668,7 @@
         <v>17</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>17</v>
@@ -10637,10 +10677,10 @@
         <v>17</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>17</v>
+        <v>533</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>106</v>
+        <v>534</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>17</v>
@@ -10651,46 +10691,42 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>464</v>
+        <v>17</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>465</v>
+        <v>103</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>17</v>
       </c>
@@ -10738,19 +10774,19 @@
         <v>17</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>17</v>
@@ -10762,7 +10798,7 @@
         <v>17</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>17</v>
@@ -10773,21 +10809,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>17</v>
@@ -10796,23 +10832,21 @@
         <v>17</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>236</v>
+        <v>109</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>529</v>
+        <v>110</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>530</v>
+        <v>111</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>17</v>
       </c>
@@ -10836,13 +10870,13 @@
         <v>17</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>250</v>
+        <v>17</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>251</v>
+        <v>17</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>17</v>
@@ -10860,34 +10894,34 @@
         <v>17</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>116</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>532</v>
+        <v>17</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>254</v>
+        <v>17</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>255</v>
+        <v>106</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>256</v>
+        <v>17</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>17</v>
@@ -10895,45 +10929,45 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>17</v>
+        <v>474</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>534</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>535</v>
+        <v>475</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>377</v>
+        <v>476</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>536</v>
+        <v>112</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>379</v>
+        <v>194</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>17</v>
@@ -10982,37 +11016,37 @@
         <v>17</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>533</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>537</v>
+        <v>17</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>383</v>
+        <v>17</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>384</v>
+        <v>187</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>385</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -11028,7 +11062,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
@@ -11040,7 +11074,7 @@
         <v>17</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>236</v>
@@ -11055,7 +11089,7 @@
         <v>541</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>390</v>
+        <v>249</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>17</v>
@@ -11080,13 +11114,13 @@
         <v>17</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>391</v>
+        <v>250</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>392</v>
+        <v>251</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>17</v>
@@ -11107,13 +11141,13 @@
         <v>538</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>100</v>
@@ -11122,16 +11156,16 @@
         <v>17</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>17</v>
+        <v>542</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>187</v>
+        <v>254</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>394</v>
+        <v>255</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>17</v>
@@ -11139,21 +11173,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>396</v>
+        <v>17</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>17</v>
@@ -11162,22 +11196,22 @@
         <v>17</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>236</v>
+        <v>544</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>397</v>
+        <v>545</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>399</v>
+        <v>546</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>17</v>
@@ -11202,13 +11236,13 @@
         <v>17</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>401</v>
+        <v>17</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>402</v>
+        <v>17</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>17</v>
@@ -11226,13 +11260,13 @@
         <v>17</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>17</v>
@@ -11244,27 +11278,27 @@
         <v>17</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>403</v>
+        <v>547</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>406</v>
+        <v>386</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11275,7 +11309,7 @@
         <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>17</v>
@@ -11287,19 +11321,19 @@
         <v>17</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>17</v>
+        <v>236</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>456</v>
+        <v>551</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>457</v>
+        <v>400</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>17</v>
@@ -11324,13 +11358,13 @@
         <v>17</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>17</v>
+        <v>401</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>17</v>
+        <v>402</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>17</v>
@@ -11348,16 +11382,16 @@
         <v>17</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>17</v>
+        <v>403</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>100</v>
@@ -11369,20 +11403,264 @@
         <v>17</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>459</v>
+        <v>187</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>460</v>
+        <v>404</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP77" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP77">
+  <autoFilter ref="A1:AP79">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11392,7 +11670,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKStillstatus.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKStillstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11</t>
+    <t>2025-12-17</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKStillstatus.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKStillstatus.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>0.0.1-rc</t>
   </si>
   <si>
     <t>Name</t>
